--- a/tame_output/ON/bt/strategyON_20240326.xlsx
+++ b/tame_output/ON/bt/strategyON_20240326.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-391.6%</t>
+          <t>-391.7%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.1%</t>
+          <t>-160.2%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.29991811929684</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153009</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537428</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310983</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309728</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.83937087185873</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575953</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430984</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568103</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963415</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.752490450168319</v>
+        <v>3.752490450168315</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.300257041161656</v>
+        <v>-2.300901503765237</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.160862406162875</v>
+        <v>2.160604621121442</v>
       </c>
       <c r="F1914" t="n">
         <v>0.8764953191285073</v>

--- a/tame_output/ON/bt/strategyON_20240326.xlsx
+++ b/tame_output/ON/bt/strategyON_20240326.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.1%</t>
+          <t>-66.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.3%</t>
+          <t>-60.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>503.4%</t>
+          <t>499.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-391.7%</t>
+          <t>-392.2%</t>
         </is>
       </c>
     </row>
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.2%</t>
+          <t>-160.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>154.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-136.3%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-85.3%</t>
+          <t>-96.7%</t>
         </is>
       </c>
     </row>
@@ -45395,10 +45395,10 @@
         <v>1.581809788230438</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.1274073780389908</v>
+        <v>-0.06319229663416204</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.227592431785391</v>
+        <v>3.113232626981499</v>
       </c>
     </row>
     <row r="1907">
@@ -45418,10 +45418,10 @@
         <v>1.694316048927529</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.3764071767225715</v>
+        <v>0.1858075020494186</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.389898652219198</v>
+        <v>3.275538847415306</v>
       </c>
     </row>
     <row r="1908">
@@ -45441,10 +45441,10 @@
         <v>1.642891749272686</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.5677862515835116</v>
+        <v>0.3771865769103587</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.376750167536544</v>
+        <v>3.262390362732652</v>
       </c>
     </row>
     <row r="1909">
@@ -45464,10 +45464,10 @@
         <v>1.803047009412023</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.5677862515835116</v>
+        <v>0.3771865769103587</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.42529450941363</v>
+        <v>3.310934704609738</v>
       </c>
     </row>
     <row r="1910">
@@ -45487,10 +45487,10 @@
         <v>1.917121291266343</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.7496029126934374</v>
+        <v>0.5590032380202845</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.53776351806558</v>
+        <v>3.423403713261688</v>
       </c>
     </row>
     <row r="1911">
@@ -45510,10 +45510,10 @@
         <v>1.959164267586893</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6858956444553544</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.605184975673144</v>
+        <v>3.490825170869252</v>
       </c>
     </row>
     <row r="1912">
@@ -45533,10 +45533,10 @@
         <v>2.02723865865577</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6858956444553544</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.59822436357805</v>
+        <v>3.483864558774159</v>
       </c>
     </row>
     <row r="1913">
@@ -45556,10 +45556,10 @@
         <v>2.138560370418457</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6858956444553544</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.612686717959193</v>
+        <v>3.498326913155302</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.752490450168315</v>
+        <v>3.467551474667201</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.300901503765237</v>
+        <v>-2.306452457606364</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.160604621121442</v>
+        <v>2.158384239584991</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6858956444553544</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.607218838418389</v>
+        <v>3.492859033614497</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240326.xlsx
+++ b/tame_output/ON/bt/strategyON_20240326.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>51.1%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-66.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.9%</t>
+          <t>106.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.0%</t>
+          <t>121.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-543.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.3%</t>
+          <t>-43.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.8%</t>
+          <t>-60.7%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.8%</t>
+          <t>88.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.4%</t>
+          <t>508.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-0.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-392.2%</t>
+          <t>-395.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>31.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-217.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-51.4%</t>
+          <t>-49.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.4%</t>
+          <t>-161.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-8.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>154.4%</t>
+          <t>-33.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-136.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.49</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-96.7%</t>
+          <t>-85.3%</t>
         </is>
       </c>
     </row>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.4357344772398012</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.331448623192657</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.4407720679673878</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.33204109966903</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43894,10 +43894,10 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.384302436791091</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.288199628822249</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43917,10 +43917,10 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.3185350467416789</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.262910281932954</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43940,10 +43940,10 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.3049995629649693</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.248124120410026</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>0.2232276625372177</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.205498086194163</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>0.15601855466534</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.183379759879115</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44009,10 +44009,10 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>0.1600100074605302</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.182801137116431</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.2381384234927305</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>3.02146865624019</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.4597603570508479</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.932686099415865</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.6677644154039252</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.854376620628559</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-0.9381643781128105</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.741298091882993</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.277322755701333</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.598719040154033</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.605339977428812</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.48785044120181</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44170,10 +44170,10 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.60200323091984</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.497283890213967</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-1.968714282586386</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.351705861591081</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.353894673516458</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.196176244031915</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.697577446743121</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>2.060472258195866</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.055227796981469</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.913518176756785</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.061888737203617</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.912626727368185</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.493694530353405</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.726237297575675</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44331,10 +44331,10 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-3.820127059221148</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.583949061030668</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-3.821691210331451</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.581903992242512</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.185317455231765</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.442941054516628</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.182890390703046</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.443166395333947</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.591479167883724</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.278492428476435</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.004461652024818</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>1.108484867291458</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.420853526311816</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.9399221681855363</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-5.79753053684166</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.7995100546422775</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-5.811245401166771</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.790123674057928</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.124070200411751</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.6633986744149372</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.128883238877088</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.6652524349580102</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.562232346987324</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.4878864871795128</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-6.945233735729955</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.3345838303608764</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.320219061901232</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.1871612158637954</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.679749384405234</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>0.04869939016024505</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.006149413070247</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.07394460134858249</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-7.999673266276687</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.06831239200938999</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-7.995982341320276</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.06683602202682515</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.200240516650139</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.1430260950401281</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.323727626592857</v>
+        <v>-8.360879543138504</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1879383845327793</v>
+        <v>-0.2027991511510381</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.250257794925409</v>
+        <v>-8.287409711471055</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1431787503723787</v>
+        <v>-0.1580395169906375</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.425382212311952</v>
+        <v>-8.462534128857598</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1986732965794795</v>
+        <v>-0.2135340631977378</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.659834306326442</v>
+        <v>-8.696986222872088</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2996732990868711</v>
+        <v>-0.3145340657051299</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.679998947875989</v>
+        <v>-8.717150864421635</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3144113464806662</v>
+        <v>-0.3292721130989249</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.140908962679956</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.909823395039814</v>
+        <v>-8.94697531158546</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4052253355076401</v>
+        <v>-0.4200861021258984</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.303556499750117</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.846754162733474</v>
+        <v>-8.88390607927912</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3773039139559891</v>
+        <v>-0.3921646805742478</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.332070062432351</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.79473864876466</v>
+        <v>-8.831890565310307</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3525073726820631</v>
+        <v>-0.3673681393003214</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.332070062432351</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.876030578318865</v>
+        <v>-8.913182494864511</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.3864993714024867</v>
+        <v>-0.401360138020745</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.332070062432351</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.678761172590868</v>
+        <v>-8.715913089136514</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.2925381989464153</v>
+        <v>-0.3073989655646741</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.134800656704353</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.479609065353769</v>
+        <v>-8.516760981899415</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.225928489698259</v>
+        <v>-0.2407892563165173</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.96947813075454</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.253763912634358</v>
+        <v>-8.290915829180005</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.1260113555742861</v>
+        <v>-0.1408721221925444</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.927551455167376</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.967489100311664</v>
+        <v>-8.00464101685731</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.01036228608914946</v>
+        <v>-0.02522305270740821</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.927551455167376</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.74069327323833</v>
+        <v>-7.777845189783975</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.08298981890229173</v>
+        <v>0.06812905228403343</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.859437510545832</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.456784542309581</v>
+        <v>-7.493936458855226</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.2022870155124279</v>
+        <v>0.1874262488941696</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.859437510545832</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.209797292116629</v>
+        <v>-7.246949208662274</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.2913446531957438</v>
+        <v>0.276483886577485</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.61245026035288</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.94596042491256</v>
+        <v>-6.983112341458205</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.3869959187644638</v>
+        <v>0.3721351521462051</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.61245026035288</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.678718624044163</v>
+        <v>-6.715870540589808</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.4920580786124487</v>
+        <v>0.4771973119941904</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.61245026035288</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.402909460643679</v>
+        <v>-6.440061377189324</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6020814289991816</v>
+        <v>0.5872206623809229</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.523430952074146</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.133841872876699</v>
+        <v>-6.170993789422345</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.7103769702514668</v>
+        <v>0.6955162036332085</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.254363364307167</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.869781934553903</v>
+        <v>-5.906933851099549</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.8027406294188331</v>
+        <v>0.7878798628005748</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9903034259843706</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.162702311049065</v>
+        <v>-5.19985422759471</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.082785445160467</v>
+        <v>1.067924678542209</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9903034259843706</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.913061281063113</v>
+        <v>-4.950213197608758</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.18298548104269</v>
+        <v>1.168124714424431</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.7406623959984189</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.658519381722037</v>
+        <v>-4.695671298267682</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.284169061999877</v>
+        <v>1.269308295381619</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.4861204966573434</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.425038159492439</v>
+        <v>-4.462190076038084</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.385485979729569</v>
+        <v>1.37062521311131</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.2526392744277448</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.245329629348566</v>
+        <v>-4.282481545894211</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.454477181474159</v>
+        <v>1.4396164148559</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.1954677702650487</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.11305415571768</v>
+        <v>-4.150206072263325</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.50275485767354</v>
+        <v>1.487894091055282</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.06319229663416204</v>
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.922454481044527</v>
+        <v>-3.959606397590172</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.581809788230438</v>
+        <v>1.56694902161218</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.06319229663416204</v>
+        <v>0.1274073780389908</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.113232626981499</v>
+        <v>3.227592431785391</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.673454682360946</v>
+        <v>-3.710606598906592</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.694316048927529</v>
+        <v>1.679455282309271</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.1858075020494186</v>
+        <v>0.3764071767225715</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.275538847415306</v>
+        <v>3.389898652219198</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.482075607500006</v>
+        <v>-3.519227524045652</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.642891749272686</v>
+        <v>1.628030982654428</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.3771865769103587</v>
+        <v>0.5677862515835116</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.262390362732652</v>
+        <v>3.376750167536544</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.20304831184438</v>
+        <v>-3.240200228390025</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.803047009412023</v>
+        <v>1.788186242793765</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.3771865769103587</v>
+        <v>0.5677862515835116</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.310934704609738</v>
+        <v>3.42529450941363</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.926310137173567</v>
+        <v>-2.963462053719212</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.917121291266343</v>
+        <v>1.902260524648085</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.5590032380202845</v>
+        <v>0.7496029126934374</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.423403713261688</v>
+        <v>3.53776351806558</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.799417730738497</v>
+        <v>-2.836569647284143</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.959164267586893</v>
+        <v>1.944303500968634</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.8764953191285073</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.490825170869252</v>
+        <v>3.605184975673144</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.611830222828571</v>
+        <v>-2.648982139374216</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.02723865865577</v>
+        <v>2.012377892037512</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.8764953191285073</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.483864558774159</v>
+        <v>3.59822436357805</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.369681829374712</v>
+        <v>-2.406833745920358</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.138560370418457</v>
+        <v>2.123699603800199</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.8764953191285073</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.498326913155302</v>
+        <v>3.612686717959193</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.467551474667201</v>
+        <v>3.792057933464529</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.306452457606364</v>
+        <v>-2.343604374152009</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.158384239584991</v>
+        <v>2.143523472966733</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.8764953191285073</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.492859033614497</v>
+        <v>3.607218838418389</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240326.xlsx
+++ b/tame_output/ON/bt/strategyON_20240326.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -615,11 +615,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>51.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>72.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.8%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.5%</t>
+          <t>-67.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,11 +973,11 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-543.6%</t>
+          <t>-544.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.7%</t>
+          <t>-61.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>508.8%</t>
+          <t>510.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.4%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-395.9%</t>
+          <t>-403.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.7%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,11 +1131,11 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-217.8%</t>
+          <t>-218.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-33.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-49.7%</t>
+          <t>-49.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>92.2%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.9%</t>
+          <t>-164.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.5%</t>
+          <t>-11.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-33.2%</t>
+          <t>155.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-136.3%</t>
+          <t>-155.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.7%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,17 +1418,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-25</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-85.3%</t>
+          <t>-139.9%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1914"/>
+  <dimension ref="A1:G1915"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43842,16 +43842,16 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386096</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4357344772398012</v>
+        <v>0.4232075093455265</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.331448623192657</v>
+        <v>3.326437836034948</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43865,16 +43865,16 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998562</v>
+        <v>3.367370539998563</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4407720679673878</v>
+        <v>0.4282451000731131</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.33204109966903</v>
+        <v>3.327030312511321</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.384302436791091</v>
+        <v>0.3717754688968163</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.288199628822249</v>
+        <v>3.283188841664539</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757924</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3185350467416789</v>
+        <v>0.3060080788474042</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.262910281932954</v>
+        <v>3.257899494775244</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760742</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3049995629649693</v>
+        <v>0.2924725950706946</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.248124120410026</v>
+        <v>3.243113333252316</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43963,10 +43963,10 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2232276625372177</v>
+        <v>0.2107006946429429</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.205498086194163</v>
+        <v>3.200487299036453</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43986,10 +43986,10 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.15601855466534</v>
+        <v>0.1434915867710653</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.183379759879115</v>
+        <v>3.178368972721405</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201489</v>
+        <v>3.29550733020149</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1600100074605302</v>
+        <v>0.1474830395662555</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.182801137116431</v>
+        <v>3.177790349958721</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44032,10 +44032,10 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2381384234927305</v>
+        <v>-0.2506653913870052</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.02146865624019</v>
+        <v>3.01645786908248</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44055,10 +44055,10 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4597603570508479</v>
+        <v>-0.4722873249451227</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.932686099415865</v>
+        <v>2.927675312258155</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44078,10 +44078,10 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6677644154039252</v>
+        <v>-0.6802913832981998</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.854376620628559</v>
+        <v>2.849365833470849</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44101,10 +44101,10 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9381643781128105</v>
+        <v>-0.9506913460070852</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.741298091882993</v>
+        <v>2.736287304725283</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44124,10 +44124,10 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.277322755701333</v>
+        <v>-1.289849723595607</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.598719040154033</v>
+        <v>2.593708252996323</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44147,10 +44147,10 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.605339977428812</v>
+        <v>-1.617866945323087</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.48785044120181</v>
+        <v>2.4828396540441</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.60200323091984</v>
+        <v>-1.614530198814115</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.497283890213967</v>
+        <v>2.492273103056257</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44193,10 +44193,10 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.968714282586386</v>
+        <v>-1.981241250480661</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.351705861591081</v>
+        <v>2.346695074433371</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44216,10 +44216,10 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.353894673516458</v>
+        <v>-2.366421641410733</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.196176244031915</v>
+        <v>2.191165456874205</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44239,10 +44239,10 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.697577446743121</v>
+        <v>-2.710104414637396</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.060472258195866</v>
+        <v>2.055461471038156</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44262,10 +44262,10 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.055227796981469</v>
+        <v>-3.067754764875744</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.913518176756785</v>
+        <v>1.908507389599075</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44285,10 +44285,10 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.061888737203617</v>
+        <v>-3.074415705097892</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.912626727368185</v>
+        <v>1.907615940210476</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.493694530353405</v>
+        <v>-3.50622149824768</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.726237297575675</v>
+        <v>1.721226510417965</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.820127059221148</v>
+        <v>-3.832654027115423</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.583949061030668</v>
+        <v>1.578938273872958</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.821691210331451</v>
+        <v>-3.834218178225726</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.581903992242512</v>
+        <v>1.576893205084802</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.185317455231765</v>
+        <v>-4.197844423126039</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.442941054516628</v>
+        <v>1.437930267358918</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.182890390703046</v>
+        <v>-4.195417358597321</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.443166395333947</v>
+        <v>1.438155608176237</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.591479167883724</v>
+        <v>-4.604006135777999</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.278492428476435</v>
+        <v>1.273481641318725</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.004461652024818</v>
+        <v>-5.016988619919093</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.108484867291458</v>
+        <v>1.103474080133748</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.420853526311816</v>
+        <v>-5.43338049420609</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9399221681855363</v>
+        <v>0.9349113810278262</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.79753053684166</v>
+        <v>-5.810057504735934</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7995100546422775</v>
+        <v>0.7944992674845675</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.811245401166771</v>
+        <v>-5.823772369061046</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.790123674057928</v>
+        <v>0.7851128869002184</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.124070200411751</v>
+        <v>-6.136597168306025</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6633986744149372</v>
+        <v>0.6583878872572275</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.128883238877088</v>
+        <v>-6.141410206771362</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6652524349580102</v>
+        <v>0.6602416478003006</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.562232346987324</v>
+        <v>-6.574759314881598</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4878864871795128</v>
+        <v>0.4828757000218031</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.945233735729955</v>
+        <v>-6.957760703624229</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3345838303608764</v>
+        <v>0.3295730432031667</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.320219061901232</v>
+        <v>-7.332746029795507</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1871612158637954</v>
+        <v>0.1821504287060858</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.679749384405234</v>
+        <v>-7.692276352299508</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.04869939016024505</v>
+        <v>0.04368860300253541</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.006149413070247</v>
+        <v>-8.018676380964521</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.07394460134858249</v>
+        <v>-0.07895538850629213</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.999673266276687</v>
+        <v>-8.012200234170962</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.06831239200938999</v>
+        <v>-0.07332317916709963</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.995982341320276</v>
+        <v>-8.008509309214549</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.06683602202682515</v>
+        <v>-0.07184680918453479</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.200240516650139</v>
+        <v>-8.212767484544411</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1430260950401281</v>
+        <v>-0.1480368821978377</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.360879543138504</v>
+        <v>-8.373406511032776</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2027991511510381</v>
+        <v>-0.2078099383087477</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.287409711471055</v>
+        <v>-8.299936679365327</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1580395169906375</v>
+        <v>-0.1630503041483471</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.462534128857598</v>
+        <v>-8.475061096751871</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2135340631977378</v>
+        <v>-0.2185448503554475</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.696986222872088</v>
+        <v>-8.70951319076636</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3145340657051299</v>
+        <v>-0.3195448528628395</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.717150864421635</v>
+        <v>-8.729677832315907</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3292721130989249</v>
+        <v>-0.3342829002566345</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.140908962679956</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.94697531158546</v>
+        <v>-8.959502279479732</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4200861021258984</v>
+        <v>-0.425096889283608</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.303556499750117</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.88390607927912</v>
+        <v>-8.896433047173392</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3921646805742478</v>
+        <v>-0.3971754677319574</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.332070062432351</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.831890565310307</v>
+        <v>-8.844417533204579</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3673681393003214</v>
+        <v>-0.3723789264580315</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.332070062432351</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.913182494864511</v>
+        <v>-8.925709462758784</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.401360138020745</v>
+        <v>-0.4063709251784546</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.332070062432351</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.715913089136514</v>
+        <v>-8.728440057030786</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.3073989655646741</v>
+        <v>-0.3124097527223837</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.134800656704353</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.516760981899415</v>
+        <v>-8.529287949793687</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.2407892563165173</v>
+        <v>-0.2458000434742269</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.96947813075454</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.290915829180005</v>
+        <v>-8.303442797074277</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.1408721221925444</v>
+        <v>-0.1458829093502545</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.927551455167376</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.00464101685731</v>
+        <v>-8.017167984751582</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.02522305270740821</v>
+        <v>-0.03023383986511741</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.927551455167376</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.777845189783975</v>
+        <v>-7.790372157678249</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.06812905228403343</v>
+        <v>0.06311826512632379</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.859437510545832</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.493936458855226</v>
+        <v>-7.5064634267495</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.1874262488941696</v>
+        <v>0.1824154617364595</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.859437510545832</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.246949208662274</v>
+        <v>-7.259476176556547</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.276483886577485</v>
+        <v>0.2714730994197754</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.61245026035288</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.983112341458205</v>
+        <v>-6.995639309352478</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.3721351521462051</v>
+        <v>0.3671243649884954</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.61245026035288</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.715870540589808</v>
+        <v>-6.728397508484082</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.4771973119941904</v>
+        <v>0.4721865248364803</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.61245026035288</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781948</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.440061377189324</v>
+        <v>-6.452588345083598</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.5872206623809229</v>
+        <v>0.5822098752232132</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.523430952074146</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567243</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.170993789422345</v>
+        <v>-6.183520757316618</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.6955162036332085</v>
+        <v>0.6905054164754989</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.254363364307167</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.906933851099549</v>
+        <v>-5.919460818993822</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.7878798628005748</v>
+        <v>0.7828690756428651</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9903034259843706</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.19985422759471</v>
+        <v>-5.212381195488984</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.067924678542209</v>
+        <v>1.0629138913845</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9903034259843706</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.950213197608758</v>
+        <v>-4.962740165503032</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.168124714424431</v>
+        <v>1.163113927266722</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.7406623959984189</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096475</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.695671298267682</v>
+        <v>-4.708198266161956</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.269308295381619</v>
+        <v>1.264297508223909</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.4861204966573434</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.462190076038084</v>
+        <v>-4.474717043932357</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.37062521311131</v>
+        <v>1.365614425953601</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.2526392744277448</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255784</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.282481545894211</v>
+        <v>-4.295008513788485</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.4396164148559</v>
+        <v>1.434605627698191</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.1954677702650487</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.150206072263325</v>
+        <v>-4.162733040157598</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.487894091055282</v>
+        <v>1.482883303897572</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.06319229663416204</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.959606397590172</v>
+        <v>-3.972133365484446</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.56694902161218</v>
+        <v>1.56193823445447</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.1274073780389908</v>
+        <v>-0.06319229663416204</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.227592431785391</v>
+        <v>3.113232626981499</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430984</v>
+        <v>3.753878996430986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.710606598906592</v>
+        <v>-3.723133566800865</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.679455282309271</v>
+        <v>1.674444495151561</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.3764071767225715</v>
+        <v>0.1858075020494186</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.389898652219198</v>
+        <v>3.275538847415306</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.519227524045652</v>
+        <v>-3.531754491939925</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.628030982654428</v>
+        <v>1.623020195496718</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.5677862515835116</v>
+        <v>0.3771865769103587</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.376750167536544</v>
+        <v>3.262390362732652</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.240200228390025</v>
+        <v>-3.252727196284298</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.788186242793765</v>
+        <v>1.783175455636055</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.5677862515835116</v>
+        <v>0.3771865769103587</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.42529450941363</v>
+        <v>3.310934704609738</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.963462053719212</v>
+        <v>-2.975989021613486</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.902260524648085</v>
+        <v>1.897249737490375</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.7496029126934374</v>
+        <v>0.5590032380202845</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.53776351806558</v>
+        <v>3.423403713261688</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.836569647284143</v>
+        <v>-2.849096615178416</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.944303500968634</v>
+        <v>1.939292713810925</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6858956444553544</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.605184975673144</v>
+        <v>3.490825170869252</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.648982139374216</v>
+        <v>-2.661509107268489</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.012377892037512</v>
+        <v>2.007367104879802</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6858956444553544</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.59822436357805</v>
+        <v>3.483864558774159</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963415</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.406833745920358</v>
+        <v>-2.419360713814631</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.123699603800199</v>
+        <v>2.118688816642488</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6858956444553544</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.612686717959193</v>
+        <v>3.498326913155302</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,45 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.792057933464529</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.343604374152009</v>
+        <v>-2.417916602086727</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.143523472966733</v>
+        <v>2.113798581792845</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.8764953191285073</v>
+        <v>0.6858956444553544</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.607218838418389</v>
+        <v>3.492859033614497</v>
+      </c>
+    </row>
+    <row r="1915">
+      <c r="A1915" s="2" t="n">
+        <v>45377</v>
+      </c>
+      <c r="B1915" t="n">
+        <v>3.793650276027314</v>
+      </c>
+      <c r="C1915" t="n">
+        <v>3.068346350536407</v>
+      </c>
+      <c r="D1915" t="n">
+        <v>-2.417916602086727</v>
+      </c>
+      <c r="E1915" t="n">
+        <v>2.113798581792845</v>
+      </c>
+      <c r="F1915" t="n">
+        <v>0.6858956444553544</v>
+      </c>
+      <c r="G1915" t="n">
+        <v>3.061410147522774</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240326.xlsx
+++ b/tame_output/ON/bt/strategyON_20240326.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -671,17 +671,17 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.3%</t>
+          <t>21.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.1%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-26</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-30.7%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>49.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>23.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-25.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.0%</t>
+          <t>-67.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.0%</t>
+          <t>105.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.3%</t>
+          <t>120.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-544.8%</t>
+          <t>-539.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.5%</t>
+          <t>-43.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-61.2%</t>
+          <t>-62.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>88.0%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>510.9%</t>
+          <t>499.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-403.4%</t>
+          <t>-412.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.9%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.59</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-218.3%</t>
+          <t>-216.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.8%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>26.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-49.2%</t>
+          <t>-50.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>98.5%</t>
+          <t>77.5%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-164.8%</t>
+          <t>-168.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.5%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.18</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>155.8%</t>
+          <t>129.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-155.4%</t>
+          <t>-156.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>71.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-160.8%</t>
         </is>
       </c>
     </row>
@@ -43848,10 +43848,10 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4232075093455265</v>
+        <v>0.4728863937854478</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.326437836034948</v>
+        <v>3.346309389810916</v>
       </c>
       <c r="F1839" t="n">
         <v>1.818391164641208</v>
@@ -43871,10 +43871,10 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4282451000731131</v>
+        <v>0.4779239845130344</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.327030312511321</v>
+        <v>3.346901866287289</v>
       </c>
       <c r="F1840" t="n">
         <v>1.874035620907526</v>
@@ -43888,16 +43888,16 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082127</v>
+        <v>3.299560092082128</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.3717754688968163</v>
+        <v>0.4214543533367376</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.283188841664539</v>
+        <v>3.303060395440507</v>
       </c>
       <c r="F1841" t="n">
         <v>1.817565989731229</v>
@@ -43911,16 +43911,16 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757925</v>
+        <v>3.293490533757926</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3060080788474042</v>
+        <v>0.3556869632873255</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.257899494775244</v>
+        <v>3.277771048551212</v>
       </c>
       <c r="F1842" t="n">
         <v>1.817565989731229</v>
@@ -43934,16 +43934,16 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760743</v>
+        <v>3.293766719760744</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.2924725950706946</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.243113333252316</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
         <v>1.817565989731229</v>
@@ -43957,16 +43957,16 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706672</v>
+        <v>3.298730590706673</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2107006946429429</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.200487299036453</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
         <v>1.844601563137365</v>
@@ -43980,16 +43980,16 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296839</v>
+        <v>3.299918119296841</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1434915867710653</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.178368972721405</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
         <v>1.844601563137365</v>
@@ -44003,16 +44003,16 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.29550733020149</v>
+        <v>3.295507330201492</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1474830395662555</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.177790349958721</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
         <v>1.848593015932555</v>
@@ -44026,16 +44026,16 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153008</v>
+        <v>3.25879198115301</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2506653913870052</v>
+        <v>-0.2009865069470839</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.01645786908248</v>
+        <v>3.036329422858449</v>
       </c>
       <c r="F1847" t="n">
         <v>1.450444584979295</v>
@@ -44049,16 +44049,16 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537427</v>
+        <v>3.271168579537429</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4722873249451227</v>
+        <v>-0.4226084405052014</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.927675312258155</v>
+        <v>2.947546866034124</v>
       </c>
       <c r="F1848" t="n">
         <v>1.412918451291926</v>
@@ -44072,16 +44072,16 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382192</v>
+        <v>3.272760131382193</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6802913832981998</v>
+        <v>-0.6306124988582786</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.849365833470849</v>
+        <v>2.869237387246818</v>
       </c>
       <c r="F1849" t="n">
         <v>1.412918451291926</v>
@@ -44095,16 +44095,16 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074625</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.9506913460070852</v>
+        <v>-0.901012461567164</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.736287304725283</v>
+        <v>2.756158858501252</v>
       </c>
       <c r="F1850" t="n">
         <v>1.14251848858304</v>
@@ -44118,16 +44118,16 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911641</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.289849723595607</v>
+        <v>-1.240170839155686</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.593708252996323</v>
+        <v>2.613579806772292</v>
       </c>
       <c r="F1851" t="n">
         <v>0.8033601109945183</v>
@@ -44141,16 +44141,16 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213498</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.617866945323087</v>
+        <v>-1.568188060883165</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.4828396540441</v>
+        <v>2.502711207820068</v>
       </c>
       <c r="F1852" t="n">
         <v>0.4753428892670392</v>
@@ -44164,16 +44164,16 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416047</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.614530198814115</v>
+        <v>-1.564851314374194</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.492273103056257</v>
+        <v>2.512144656832226</v>
       </c>
       <c r="F1853" t="n">
         <v>0.4780349216860705</v>
@@ -44187,16 +44187,16 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.981241250480661</v>
+        <v>-1.931562366040739</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.346695074433371</v>
+        <v>2.366566628209339</v>
       </c>
       <c r="F1854" t="n">
         <v>0.1113238700195249</v>
@@ -44210,16 +44210,16 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.278199702495501</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.366421641410733</v>
+        <v>-2.316742756970812</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.191165456874205</v>
+        <v>2.211037010650174</v>
       </c>
       <c r="F1855" t="n">
         <v>0.1113238700195249</v>
@@ -44233,16 +44233,16 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347058</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.710104414637396</v>
+        <v>-2.660425530197474</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.055461471038156</v>
+        <v>2.075333024814125</v>
       </c>
       <c r="F1856" t="n">
         <v>0.003417817992306726</v>
@@ -44256,16 +44256,16 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.28737757613002</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.067754764875744</v>
+        <v>-3.018075880435823</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.908507389599075</v>
+        <v>1.928378943375043</v>
       </c>
       <c r="F1857" t="n">
         <v>-0.3542325322460414</v>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178246</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.074415705097892</v>
+        <v>-3.02473682065797</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.907615940210476</v>
+        <v>1.927487493986444</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.3542325322460414</v>
@@ -44302,16 +44302,16 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207815</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.50622149824768</v>
+        <v>-3.456542613807758</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.721226510417965</v>
+        <v>1.741098064193933</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.4906500286873084</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310984</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.832654027115423</v>
+        <v>-3.782975142675502</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.578938273872958</v>
+        <v>1.598809827648927</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.5731182791944566</v>
@@ -44348,16 +44348,16 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.834218178225726</v>
+        <v>-3.784539293785805</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.576893205084802</v>
+        <v>1.596764758860771</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.5731182791944566</v>
@@ -44371,16 +44371,16 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.197844423126039</v>
+        <v>-4.148165538686118</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.437930267358918</v>
+        <v>1.457801821134887</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.6713399160615824</v>
@@ -44394,16 +44394,16 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.195417358597321</v>
+        <v>-4.145738474157399</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.438155608176237</v>
+        <v>1.458027161952206</v>
       </c>
       <c r="F1863" t="n">
         <v>-0.671672697868734</v>
@@ -44417,16 +44417,16 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.604006135777999</v>
+        <v>-4.554327251338078</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.273481641318725</v>
+        <v>1.293353195094693</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.080261475049412</v>
@@ -44440,16 +44440,16 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.016988619919093</v>
+        <v>-4.967309735479172</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.103474080133748</v>
+        <v>1.123345633909716</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.080261475049412</v>
@@ -44463,16 +44463,16 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.43338049420609</v>
+        <v>-5.383701609766169</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9349113810278262</v>
+        <v>0.9547829348037946</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.080261475049412</v>
@@ -44486,16 +44486,16 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.810057504735934</v>
+        <v>-5.760378620296014</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7944992674845675</v>
+        <v>0.8143708212605358</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.080261475049412</v>
@@ -44509,16 +44509,16 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.823772369061046</v>
+        <v>-5.774093484621125</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.7851128869002184</v>
+        <v>0.8049844406761864</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.080261475049412</v>
@@ -44532,16 +44532,16 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.136597168306025</v>
+        <v>-6.086918283866105</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6583878872572275</v>
+        <v>0.6782594410331955</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.080261475049412</v>
@@ -44555,16 +44555,16 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.141410206771362</v>
+        <v>-6.091731322331442</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.6602416478003006</v>
+        <v>0.680113201576269</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.081808109752198</v>
@@ -44578,16 +44578,16 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.574759314881598</v>
+        <v>-6.525080430441678</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.4828757000218031</v>
+        <v>0.5027472537977715</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.081808109752198</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297753</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.957760703624229</v>
+        <v>-6.908081819184309</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3295730432031667</v>
+        <v>0.3494445969791347</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.081808109752198</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.44775050131762</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.332746029795507</v>
+        <v>-7.283067145355586</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.1821504287060858</v>
+        <v>0.2020219824820542</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.456793435923476</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737174</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.692276352299508</v>
+        <v>-7.642597467859588</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.04368860300253541</v>
+        <v>0.0635601567785038</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.456793435923476</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341317</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.018676380964521</v>
+        <v>-7.968997496524601</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.07895538850629213</v>
+        <v>-0.05908383473032419</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.783193464588488</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.50044609677668</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.012200234170962</v>
+        <v>-7.962521349731041</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.07332317916709963</v>
+        <v>-0.05345162539113124</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.776717317794929</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.008509309214549</v>
+        <v>-7.95883042477463</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.07184680918453479</v>
+        <v>-0.05197525540856685</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.776717317794929</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.212767484544411</v>
+        <v>-8.163088600104492</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1480368821978377</v>
+        <v>-0.1281653284218693</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.904356262408918</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.373406511032776</v>
+        <v>-8.323727626592857</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2078099383087477</v>
+        <v>-0.1879383845327793</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.019089735411313</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.299936679365327</v>
+        <v>-8.250257794925409</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1630503041483471</v>
+        <v>-0.1431787503723787</v>
       </c>
       <c r="F1880" t="n">
         <v>-1.945619903743865</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.475061096751871</v>
+        <v>-8.425382212311952</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2185448503554475</v>
+        <v>-0.1986732965794795</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.120744321130409</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.70951319076636</v>
+        <v>-8.659834306326442</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3195448528628395</v>
+        <v>-0.2996732990868711</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.120744321130409</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.729677832315907</v>
+        <v>-8.679998947875989</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3342829002566345</v>
+        <v>-0.3144113464806662</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.140908962679956</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.959502279479732</v>
+        <v>-8.909823395039814</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.425096889283608</v>
+        <v>-0.4052253355076401</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.303556499750117</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767397</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.896433047173392</v>
+        <v>-8.846754162733474</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3971754677319574</v>
+        <v>-0.3773039139559891</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.332070062432351</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.844417533204579</v>
+        <v>-8.79473864876466</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3723789264580315</v>
+        <v>-0.3525073726820631</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.332070062432351</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.925709462758784</v>
+        <v>-8.876030578318865</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.4063709251784546</v>
+        <v>-0.3864993714024867</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.332070062432351</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.728440057030786</v>
+        <v>-8.678761172590868</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.3124097527223837</v>
+        <v>-0.2925381989464153</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.134800656704353</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240577</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.529287949793687</v>
+        <v>-8.479609065353769</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.2458000434742269</v>
+        <v>-0.225928489698259</v>
       </c>
       <c r="F1889" t="n">
         <v>-1.96947813075454</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.68515780608528</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.303442797074277</v>
+        <v>-8.253763912634358</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.1458829093502545</v>
+        <v>-0.1260113555742861</v>
       </c>
       <c r="F1890" t="n">
         <v>-1.927551455167376</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.684840248282101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.017167984751582</v>
+        <v>-7.967489100311664</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.03023383986511741</v>
+        <v>-0.01036228608914946</v>
       </c>
       <c r="F1891" t="n">
         <v>-1.927551455167376</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.790372157678249</v>
+        <v>-7.74069327323833</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.06311826512632379</v>
+        <v>0.08298981890229173</v>
       </c>
       <c r="F1892" t="n">
         <v>-1.859437510545832</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.5064634267495</v>
+        <v>-7.456784542309581</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.1824154617364595</v>
+        <v>0.2022870155124279</v>
       </c>
       <c r="F1893" t="n">
         <v>-1.859437510545832</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.259476176556547</v>
+        <v>-7.209797292116629</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.2714730994197754</v>
+        <v>0.2913446531957438</v>
       </c>
       <c r="F1894" t="n">
         <v>-1.61245026035288</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.995639309352478</v>
+        <v>-6.94596042491256</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.3671243649884954</v>
+        <v>0.3869959187644638</v>
       </c>
       <c r="F1895" t="n">
         <v>-1.61245026035288</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.728397508484082</v>
+        <v>-6.678718624044163</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.4721865248364803</v>
+        <v>0.4920580786124487</v>
       </c>
       <c r="F1896" t="n">
         <v>-1.61245026035288</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781948</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.452588345083598</v>
+        <v>-6.402909460643679</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.5822098752232132</v>
+        <v>0.6020814289991816</v>
       </c>
       <c r="F1897" t="n">
         <v>-1.523430952074146</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567243</v>
+        <v>3.800825778567245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.183520757316618</v>
+        <v>-6.133841872876699</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.6905054164754989</v>
+        <v>0.7103769702514668</v>
       </c>
       <c r="F1898" t="n">
         <v>-1.254363364307167</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.919460818993822</v>
+        <v>-5.869781934553903</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.7828690756428651</v>
+        <v>0.8027406294188331</v>
       </c>
       <c r="F1899" t="n">
         <v>-0.9903034259843706</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309729</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.212381195488984</v>
+        <v>-5.162702311049065</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.0629138913845</v>
+        <v>1.082785445160467</v>
       </c>
       <c r="F1900" t="n">
         <v>-0.9903034259843706</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.962740165503032</v>
+        <v>-4.913061281063113</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.163113927266722</v>
+        <v>1.18298548104269</v>
       </c>
       <c r="F1901" t="n">
         <v>-0.7406623959984189</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096475</v>
+        <v>3.856158176096477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.708198266161956</v>
+        <v>-4.658519381722037</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.264297508223909</v>
+        <v>1.284169061999877</v>
       </c>
       <c r="F1902" t="n">
         <v>-0.4861204966573434</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761809</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.474717043932357</v>
+        <v>-4.425038159492439</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.365614425953601</v>
+        <v>1.385485979729569</v>
       </c>
       <c r="F1903" t="n">
         <v>-0.2526392744277448</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255784</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.295008513788485</v>
+        <v>-4.245329629348566</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.434605627698191</v>
+        <v>1.454477181474159</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.1954677702650487</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.162733040157598</v>
+        <v>-4.11305415571768</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.482883303897572</v>
+        <v>1.50275485767354</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.06319229663416204</v>
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.972133365484446</v>
+        <v>-4.128379305427653</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.56193823445447</v>
+        <v>1.499439858477188</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.06319229663416204</v>
+        <v>-0.07851744634413549</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.113232626981499</v>
+        <v>3.104037537155515</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430986</v>
+        <v>3.753878996430988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.723133566800865</v>
+        <v>-3.879379506744072</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.674444495151561</v>
+        <v>1.611946119174279</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.1858075020494186</v>
+        <v>0.1704823523394452</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.275538847415306</v>
+        <v>3.266343757589322</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.531754491939925</v>
+        <v>-3.688000431883132</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.623020195496718</v>
+        <v>1.560521819519436</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.3771865769103587</v>
+        <v>0.3618614272003853</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.262390362732652</v>
+        <v>3.253195272906668</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704190084579</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.252727196284298</v>
+        <v>-3.408973136227505</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.783175455636055</v>
+        <v>1.720677079658773</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.3771865769103587</v>
+        <v>0.3618614272003853</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.310934704609738</v>
+        <v>3.301739614783754</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.975989021613486</v>
+        <v>-3.132234961556693</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.897249737490375</v>
+        <v>1.834751361513093</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.5590032380202845</v>
+        <v>0.5436780883103111</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.423403713261688</v>
+        <v>3.414208623435704</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.849096615178416</v>
+        <v>-3.005342555121623</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.939292713810925</v>
+        <v>1.876794337833643</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.670570494745381</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.490825170869252</v>
+        <v>3.481630081043268</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.661509107268489</v>
+        <v>-2.817755047211696</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.007367104879802</v>
+        <v>1.94486872890252</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.670570494745381</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.483864558774159</v>
+        <v>3.474669468948175</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.419360713814631</v>
+        <v>-2.575606653757838</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.118688816642488</v>
+        <v>2.056190440665207</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.670570494745381</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.498326913155302</v>
+        <v>3.489131823329318</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192818</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.417916602086727</v>
+        <v>-2.51237728198949</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.113798581792845</v>
+        <v>2.076014309831741</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.670570494745381</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.492859033614497</v>
+        <v>3.483663943788513</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.793650276027314</v>
+        <v>3.49102930401969</v>
       </c>
       <c r="C1915" t="n">
-        <v>3.068346350536407</v>
+        <v>2.859623366546639</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.417916602086727</v>
+        <v>-2.51237728198949</v>
       </c>
       <c r="E1915" t="n">
-        <v>2.113798581792845</v>
+        <v>2.076014309831741</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.6858956444553544</v>
+        <v>0.670570494745381</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.061410147522774</v>
+        <v>2.852687163533007</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240326.xlsx
+++ b/tame_output/ON/bt/strategyON_20240326.xlsx
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082128</v>
+        <v>3.299560092082127</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757926</v>
+        <v>3.293490533757925</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760744</v>
+        <v>3.293766719760743</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706673</v>
+        <v>3.298730590706672</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296841</v>
+        <v>3.299918119296839</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201492</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.25879198115301</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537429</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382193</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074625</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911641</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213498</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416047</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495501</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347058</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.28737757613002</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178246</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207815</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310984</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199287</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297753</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.44775050131762</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737174</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341317</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50044609677668</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880272</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234398</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860586</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792544</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410718</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240577</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.68515780608528</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282101</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906229</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567245</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487774</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309729</v>
+        <v>3.833249172309726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858731</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096477</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761809</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575954</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430988</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077644</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180809</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568107</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963418</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192818</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.49102930401969</v>
+        <v>3.491029304019688</v>
       </c>
       <c r="C1915" t="n">
         <v>2.859623366546639</v>

--- a/tame_output/ON/bt/strategyON_20240326.xlsx
+++ b/tame_output/ON/bt/strategyON_20240326.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>30.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-26</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-30.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>49.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-25.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.4%</t>
+          <t>-66.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.5%</t>
+          <t>105.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.8%</t>
+          <t>120.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.3%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.4%</t>
+          <t>-60.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.1%</t>
+          <t>499.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-412.8%</t>
+          <t>-393.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.59</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.0%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.3%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.5%</t>
+          <t>-50.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-168.6%</t>
+          <t>-161.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.18</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,32 +1318,32 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>129.7%</t>
+          <t>126.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-156.9%</t>
+          <t>-137.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>75.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>71.3%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>71.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-160.8%</t>
+          <t>-86.5%</t>
         </is>
       </c>
     </row>
@@ -45593,19 +45593,19 @@
         <v>3.491029304019688</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.859623366546639</v>
+        <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.51237728198949</v>
+        <v>-2.322131458034096</v>
       </c>
       <c r="E1915" t="n">
-        <v>2.076014309831741</v>
+        <v>2.149610733424475</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.670570494745381</v>
+        <v>0.8608163187007751</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.852687163533007</v>
+        <v>3.595309532172326</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240326.xlsx
+++ b/tame_output/ON/bt/strategyON_20240326.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>20.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.3%</t>
+          <t>-67.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.8%</t>
+          <t>106.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.9%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.3%</t>
+          <t>-44.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.3%</t>
+          <t>-61.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.9%</t>
+          <t>499.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-393.8%</t>
+          <t>-400.0%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-50.9%</t>
+          <t>-62.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>77.5%</t>
+          <t>-218.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.3%</t>
+          <t>-163.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.13</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,47 +1308,47 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-30.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>126.6%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.8%</t>
+          <t>-148.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-137.9%</t>
+          <t>-144.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.3%</t>
+          <t>73.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.8%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>71.5%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-86.5%</t>
+          <t>-90.2%</t>
         </is>
       </c>
     </row>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386096</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998563</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.272760131382192</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199287</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.679998947875989</v>
+        <v>-8.94763815086368</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.3144113464806662</v>
+        <v>-0.4214670276757428</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.140908962679956</v>
+        <v>-2.408548165667647</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.873399279375503</v>
+        <v>1.712815757582889</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.909823395039814</v>
+        <v>-9.177462598027505</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4052253355076401</v>
+        <v>-0.5122810167027163</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.303556499750117</v>
+        <v>-2.571195702737807</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.776926546971963</v>
+        <v>1.616343025179349</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.846754162733474</v>
+        <v>-9.114393365721165</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3773039139559891</v>
+        <v>-0.4843595951510657</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.332070062432351</v>
+        <v>-2.599709265420042</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.762512137991737</v>
+        <v>1.601928616199123</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.79473864876466</v>
+        <v>-9.062377851752352</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3525073726820631</v>
+        <v>-0.4595630538771398</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.332070062432351</v>
+        <v>-2.599709265420042</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.766502473678138</v>
+        <v>1.605918951885524</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.876030578318865</v>
+        <v>-9.143669781306556</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.3864993714024867</v>
+        <v>-0.4935550525975634</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.332070062432351</v>
+        <v>-2.599709265420042</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.765027246779396</v>
+        <v>1.604443724986782</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.678761172590868</v>
+        <v>-8.946400375578559</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.2925381989464153</v>
+        <v>-0.399593880141492</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.134800656704353</v>
+        <v>-2.402439859692044</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.898442300381068</v>
+        <v>1.737858778588453</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.479609065353769</v>
+        <v>-8.74724826834146</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.225928489698259</v>
+        <v>-0.3329841708933352</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.96947813075454</v>
+        <v>-2.23711733374223</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.984584682304273</v>
+        <v>1.824001160511658</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.253763912634358</v>
+        <v>-8.52140311562205</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.1260113555742861</v>
+        <v>-0.2330670367693628</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.927551455167376</v>
+        <v>-2.195190658155067</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.019319760692779</v>
+        <v>1.858736238900165</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.967489100311664</v>
+        <v>-8.235128303299355</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.01036228608914946</v>
+        <v>-0.1174179672842257</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.927551455167376</v>
+        <v>-2.195190658155067</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.020458905248838</v>
+        <v>1.859875383456224</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.74069327323833</v>
+        <v>-8.008332476226022</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.08298981890229173</v>
+        <v>-0.02406586229278496</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.859437510545832</v>
+        <v>-2.127076713533522</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.063961046183873</v>
+        <v>1.903377524391258</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.456784542309581</v>
+        <v>-7.724423745297273</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.2022870155124279</v>
+        <v>0.0952313343173512</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.859437510545832</v>
+        <v>-2.127076713533522</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.069694750422509</v>
+        <v>1.909111228629895</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.209797292116629</v>
+        <v>-7.47743649510432</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.2913446531957438</v>
+        <v>0.1842889720006671</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.61245026035288</v>
+        <v>-1.88008946334057</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.208149838144415</v>
+        <v>2.047566316351801</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.94596042491256</v>
+        <v>-7.213599627900251</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.3869959187644638</v>
+        <v>0.2799402375693871</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.61245026035288</v>
+        <v>-1.88008946334057</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.198266356831507</v>
+        <v>2.037682835038893</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.678718624044163</v>
+        <v>-6.946357827031854</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.4920580786124487</v>
+        <v>0.385002397417372</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.61245026035288</v>
+        <v>-1.88008946334057</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.196431796332134</v>
+        <v>2.03584827453952</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.402909460643679</v>
+        <v>-6.67054866363137</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6020814289991816</v>
+        <v>0.4950257478041049</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.523430952074146</v>
+        <v>-1.791070155061837</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.249543066325913</v>
+        <v>2.088959544533298</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.133841872876699</v>
+        <v>-6.401481075864391</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.7103769702514668</v>
+        <v>0.6033212890563902</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.254363364307167</v>
+        <v>-1.522002567294857</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.411652125131594</v>
+        <v>2.25106860333898</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.869781934553903</v>
+        <v>-6.137421137541595</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.8027406294188331</v>
+        <v>0.6956849482237564</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9903034259843706</v>
+        <v>-1.257942628972061</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.55682777196352</v>
+        <v>2.396244250170906</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309726</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.162702311049065</v>
+        <v>-5.430341514036757</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.082785445160467</v>
+        <v>0.9757297639653912</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9903034259843706</v>
+        <v>-1.257942628972061</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.554040738303219</v>
+        <v>2.393457216510605</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858728</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.913061281063113</v>
+        <v>-5.180700484050805</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.18298548104269</v>
+        <v>1.075929799847613</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.7406623959984189</v>
+        <v>-1.008301598986109</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.704168980182631</v>
+        <v>2.543585458390017</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096473</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.658519381722037</v>
+        <v>-4.926158584709729</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.284169061999877</v>
+        <v>1.1771133808048</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.4861204966573434</v>
+        <v>-0.753759699645034</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.856260941008034</v>
+        <v>2.695677419215419</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.425038159492439</v>
+        <v>-4.69267736248013</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.385485979729569</v>
+        <v>1.278430298534492</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.2526392744277448</v>
+        <v>-0.5202784774154354</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.004274103183645</v>
+        <v>2.84369058139103</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.245329629348566</v>
+        <v>-4.512968832336258</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.454477181474159</v>
+        <v>1.347421500279082</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.1954677702650487</v>
+        <v>-0.4631069732527393</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.035684795368303</v>
+        <v>2.875101273575689</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.11305415571768</v>
+        <v>-4.380693358705371</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.50275485767354</v>
+        <v>1.395699176478464</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.06319229663416204</v>
+        <v>-0.3308314996218527</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.110417566293862</v>
+        <v>2.949834044501248</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575953</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.128379305427653</v>
+        <v>-4.190093684032218</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.499439858477188</v>
+        <v>1.474754107035362</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.07851744634413549</v>
+        <v>-0.1402318249486998</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.104037537155515</v>
+        <v>3.067008909992777</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.879379506744072</v>
+        <v>-3.941093885348638</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.611946119174279</v>
+        <v>1.587260367732453</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.1704823523394452</v>
+        <v>0.1087679737348809</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.266343757589322</v>
+        <v>3.229315130426584</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.688000431883132</v>
+        <v>-3.749714810487698</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.560521819519436</v>
+        <v>1.53583606807761</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.3618614272003853</v>
+        <v>0.300147048595821</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.253195272906668</v>
+        <v>3.216166645743929</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.408973136227505</v>
+        <v>-3.470687514832071</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.720677079658773</v>
+        <v>1.695991328216947</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.3618614272003853</v>
+        <v>0.300147048595821</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.301739614783754</v>
+        <v>3.264710987621016</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.132234961556693</v>
+        <v>-3.193949340161259</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.834751361513093</v>
+        <v>1.810065610071267</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.5436780883103111</v>
+        <v>0.4819637097057468</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.414208623435704</v>
+        <v>3.377179996272965</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-3.005342555121623</v>
+        <v>-3.067056933726189</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.876794337833643</v>
+        <v>1.852108586391816</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.670570494745381</v>
+        <v>0.6088561161408167</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.481630081043268</v>
+        <v>3.444601453880529</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568105</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.817755047211696</v>
+        <v>-2.879469425816262</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.94486872890252</v>
+        <v>1.920182977460694</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.670570494745381</v>
+        <v>0.6088561161408167</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.474669468948175</v>
+        <v>3.437640841785436</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963418</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.575606653757838</v>
+        <v>-2.637321032362404</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.056190440665207</v>
+        <v>2.031504689223381</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.670570494745381</v>
+        <v>0.6088561161408167</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.489131823329318</v>
+        <v>3.452103196166579</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192817</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-2.51237728198949</v>
+        <v>-2.574091660594056</v>
       </c>
       <c r="E1914" t="n">
-        <v>2.076014309831741</v>
+        <v>2.051328558389915</v>
       </c>
       <c r="F1914" t="n">
-        <v>0.670570494745381</v>
+        <v>0.6088561161408167</v>
       </c>
       <c r="G1914" t="n">
-        <v>3.483663943788513</v>
+        <v>3.446635316625774</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.491029304019688</v>
+        <v>3.486558612509473</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-2.322131458034096</v>
+        <v>-2.383929536047527</v>
       </c>
       <c r="E1915" t="n">
-        <v>2.149610733424475</v>
+        <v>2.124891502219103</v>
       </c>
       <c r="F1915" t="n">
-        <v>0.8608163187007751</v>
+        <v>0.7990182406873458</v>
       </c>
       <c r="G1915" t="n">
-        <v>3.595309532172326</v>
+        <v>3.558230685364268</v>
       </c>
     </row>
   </sheetData>
